--- a/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
+++ b/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
@@ -68,13 +68,13 @@
     <t>Total Execution Time (hrs)</t>
   </si>
   <si>
-    <t>0.01</t>
+    <t>0.02</t>
   </si>
   <si>
     <t>Average Test Duration (ms)</t>
   </si>
   <si>
-    <t>50883.00</t>
+    <t>55602.00</t>
   </si>
   <si>
     <t>Date</t>
@@ -104,7 +104,7 @@
     <t>2026-05-07</t>
   </si>
   <si>
-    <t>50.88</t>
+    <t>55.60</t>
   </si>
   <si>
     <t>TOTAL</t>

--- a/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
+++ b/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
   <si>
     <t>Metric</t>
   </si>
@@ -53,34 +53,34 @@
     <t>Total Passed</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Total Failed</t>
+  </si>
+  <si>
+    <t>Total Skipped</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>Total Failed</t>
-  </si>
-  <si>
-    <t>Total Skipped</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Overall Pass Rate</t>
   </si>
   <si>
-    <t>37.50%</t>
+    <t>50.00%</t>
   </si>
   <si>
     <t>Total Execution Time (hrs)</t>
   </si>
   <si>
-    <t>0.01</t>
+    <t>0.02</t>
   </si>
   <si>
     <t>Average Test Duration (ms)</t>
   </si>
   <si>
-    <t>6513.50</t>
+    <t>8882.25</t>
   </si>
   <si>
     <t>Date</t>
@@ -110,7 +110,7 @@
     <t>2026-05-13</t>
   </si>
   <si>
-    <t>52.11</t>
+    <t>71.06</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -149,67 +149,70 @@
     <t>Error Details</t>
   </si>
   <si>
+    <t>Test 5: Signature Advance Workflow via Keyboard</t>
+  </si>
+  <si>
+    <t>chromium &gt; ui\keyboardAccessibilityTest.stage.spec.ts &gt; ⌨️  Keyboard Navigation Suite - STAGE</t>
+  </si>
+  <si>
+    <t>tests/ui/keyboardAccessibilityTest.stage.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: locator.waitFor: Target page, context or browser has been closed
+Call log:
+[2m  - waiting for locator('text="Add Recipients"') to be visible[22m
+Error: locator.waitFor: Target page, context or browser has been closed
+Call log:
+[2m  - waiting for locator('text="Add Recipients"') to be visible[22m
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:270:52</t>
+  </si>
+  <si>
+    <t>Passes</t>
+  </si>
+  <si>
+    <t>Success Rate</t>
+  </si>
+  <si>
+    <t>Avg Duration (ms)</t>
+  </si>
+  <si>
+    <t>Test 1: Home Page Keyboard Navigation</t>
+  </si>
+  <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>15483.00</t>
+  </si>
+  <si>
+    <t>Test 2: Landing Page Keyboard Navigation</t>
+  </si>
+  <si>
+    <t>42.00</t>
+  </si>
+  <si>
+    <t>Test 3: Signature Module Keyboard Navigation</t>
+  </si>
+  <si>
+    <t>17168.00</t>
+  </si>
+  <si>
     <t>Test 4: Upload Document via Keyboard</t>
   </si>
   <si>
-    <t>chromium &gt; ui\keyboardAccessibilityTest.stage.spec.ts &gt; ⌨️  Keyboard Navigation Suite - STAGE</t>
-  </si>
-  <si>
-    <t>tests/ui/keyboardAccessibilityTest.stage.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
-Call log:
-[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
-TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
-Call log:
-[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
-    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:188:52</t>
-  </si>
-  <si>
-    <t>Passes</t>
-  </si>
-  <si>
-    <t>Success Rate</t>
-  </si>
-  <si>
-    <t>Avg Duration (ms)</t>
-  </si>
-  <si>
-    <t>Test 1: Home Page Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>100.00%</t>
-  </si>
-  <si>
-    <t>16271.00</t>
-  </si>
-  <si>
-    <t>Test 2: Landing Page Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>30.00</t>
-  </si>
-  <si>
-    <t>Test 3: Signature Module Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>17584.00</t>
+    <t>24337.00</t>
   </si>
   <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>18223.00</t>
-  </si>
-  <si>
-    <t>Test 5: Signature Advance Workflow via Keyboard</t>
+    <t>14028.00</t>
+  </si>
+  <si>
+    <t>Test 6: Sign A Document via Keyboard</t>
   </si>
   <si>
     <t>0.00</t>
-  </si>
-  <si>
-    <t>Test 6: Sign A Document via Keyboard</t>
   </si>
   <si>
     <t>Test 7: Menu and Dropdown Keyboard Navigation</t>
@@ -846,16 +849,16 @@
         <v>8</v>
       </c>
       <c r="C2" s="5">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
         <v>3</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>4</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>17</v>
@@ -872,16 +875,16 @@
         <v>8</v>
       </c>
       <c r="C3" s="8">
+        <v>4</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8">
         <v>3</v>
-      </c>
-      <c r="D3" s="8">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8">
-        <v>4</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>17</v>
@@ -1144,19 +1147,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B5" s="13">
         <v>1</v>
       </c>
       <c r="C5" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="13">
-        <v>1</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>58</v>
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>59</v>
@@ -1164,19 +1167,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="13">
+        <v>1</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0</v>
+      </c>
+      <c r="D6" s="13">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>60</v>
-      </c>
-      <c r="B6" s="13">
-        <v>1</v>
-      </c>
-      <c r="C6" s="13">
-        <v>0</v>
-      </c>
-      <c r="D6" s="13">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>58</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>61</v>
@@ -1196,35 +1199,35 @@
         <v>0</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="13">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>63</v>
-      </c>
-      <c r="B8" s="13">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" s="13">
         <v>1</v>
@@ -1236,10 +1239,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
+++ b/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
   <si>
     <t>Metric</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Total Passed</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>Total Failed</t>
@@ -62,13 +62,13 @@
     <t>Total Skipped</t>
   </si>
   <si>
-    <t>3</t>
+    <t>2</t>
   </si>
   <si>
     <t>Overall Pass Rate</t>
   </si>
   <si>
-    <t>50.00%</t>
+    <t>62.50%</t>
   </si>
   <si>
     <t>Total Execution Time (hrs)</t>
@@ -80,7 +80,7 @@
     <t>Average Test Duration (ms)</t>
   </si>
   <si>
-    <t>8882.25</t>
+    <t>11232.13</t>
   </si>
   <si>
     <t>Date</t>
@@ -110,7 +110,7 @@
     <t>2026-05-13</t>
   </si>
   <si>
-    <t>71.06</t>
+    <t>89.86</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -149,76 +149,79 @@
     <t>Error Details</t>
   </si>
   <si>
+    <t>Test 6: Sign A Document via Keyboard</t>
+  </si>
+  <si>
+    <t>chromium &gt; ui\keyboardAccessibilityTest.stage.spec.ts &gt; ⌨️  Keyboard Navigation Suite - STAGE</t>
+  </si>
+  <si>
+    <t>tests/ui/keyboardAccessibilityTest.stage.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
+Call log:
+[2m  - waiting for locator('button:has-text("Prepare Document")') to be visible[22m
+TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
+Call log:
+[2m  - waiting for locator('button:has-text("Prepare Document")') to be visible[22m
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:461:53</t>
+  </si>
+  <si>
+    <t>Passes</t>
+  </si>
+  <si>
+    <t>Success Rate</t>
+  </si>
+  <si>
+    <t>Avg Duration (ms)</t>
+  </si>
+  <si>
+    <t>Test 1: Home Page Keyboard Navigation</t>
+  </si>
+  <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>14971.00</t>
+  </si>
+  <si>
+    <t>Test 2: Landing Page Keyboard Navigation</t>
+  </si>
+  <si>
+    <t>63.00</t>
+  </si>
+  <si>
+    <t>Test 3: Signature Module Keyboard Navigation</t>
+  </si>
+  <si>
+    <t>17398.00</t>
+  </si>
+  <si>
+    <t>Test 4: Upload Document via Keyboard</t>
+  </si>
+  <si>
+    <t>30404.00</t>
+  </si>
+  <si>
     <t>Test 5: Signature Advance Workflow via Keyboard</t>
   </si>
   <si>
-    <t>chromium &gt; ui\keyboardAccessibilityTest.stage.spec.ts &gt; ⌨️  Keyboard Navigation Suite - STAGE</t>
-  </si>
-  <si>
-    <t>tests/ui/keyboardAccessibilityTest.stage.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: locator.waitFor: Target page, context or browser has been closed
-Call log:
-[2m  - waiting for locator('text="Add Recipients"') to be visible[22m
-Error: locator.waitFor: Target page, context or browser has been closed
-Call log:
-[2m  - waiting for locator('text="Add Recipients"') to be visible[22m
-    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:270:52</t>
-  </si>
-  <si>
-    <t>Passes</t>
-  </si>
-  <si>
-    <t>Success Rate</t>
-  </si>
-  <si>
-    <t>Avg Duration (ms)</t>
-  </si>
-  <si>
-    <t>Test 1: Home Page Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>100.00%</t>
-  </si>
-  <si>
-    <t>15483.00</t>
-  </si>
-  <si>
-    <t>Test 2: Landing Page Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>42.00</t>
-  </si>
-  <si>
-    <t>Test 3: Signature Module Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>17168.00</t>
-  </si>
-  <si>
-    <t>Test 4: Upload Document via Keyboard</t>
-  </si>
-  <si>
-    <t>24337.00</t>
+    <t>3198.00</t>
   </si>
   <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>14028.00</t>
-  </si>
-  <si>
-    <t>Test 6: Sign A Document via Keyboard</t>
+    <t>23823.00</t>
+  </si>
+  <si>
+    <t>Test 7: Create Workflow from Templates via Keyboard</t>
   </si>
   <si>
     <t>0.00</t>
   </si>
   <si>
-    <t>Test 7: Menu and Dropdown Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>Test 8: Combined Keyboard Workflow</t>
+    <t>Test 8: Use Workflow from Templates via Keyboard</t>
   </si>
 </sst>
 </file>
@@ -849,7 +852,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -858,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>17</v>
@@ -875,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
@@ -884,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>17</v>
@@ -1167,19 +1170,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B6" s="13">
         <v>1</v>
       </c>
       <c r="C6" s="13">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13">
         <v>0</v>
       </c>
-      <c r="D6" s="13">
-        <v>1</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>60</v>
+      <c r="E6" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>61</v>
@@ -1187,7 +1190,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B7" s="13">
         <v>1</v>
@@ -1196,10 +1199,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>63</v>
@@ -1219,15 +1222,15 @@
         <v>0</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="13">
         <v>1</v>
@@ -1239,10 +1242,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
+++ b/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
   <si>
     <t>Metric</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Total Passed</t>
   </si>
   <si>
-    <t>5</t>
+    <t>3</t>
   </si>
   <si>
     <t>Total Failed</t>
@@ -62,13 +62,13 @@
     <t>Total Skipped</t>
   </si>
   <si>
-    <t>2</t>
+    <t>4</t>
   </si>
   <si>
     <t>Overall Pass Rate</t>
   </si>
   <si>
-    <t>62.50%</t>
+    <t>37.50%</t>
   </si>
   <si>
     <t>Total Execution Time (hrs)</t>
@@ -80,7 +80,7 @@
     <t>Average Test Duration (ms)</t>
   </si>
   <si>
-    <t>11232.13</t>
+    <t>6759.13</t>
   </si>
   <si>
     <t>Date</t>
@@ -110,7 +110,7 @@
     <t>2026-05-13</t>
   </si>
   <si>
-    <t>89.86</t>
+    <t>54.07</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -149,22 +149,22 @@
     <t>Error Details</t>
   </si>
   <si>
-    <t>Test 6: Sign A Document via Keyboard</t>
-  </si>
-  <si>
-    <t>chromium &gt; ui\keyboardAccessibilityTest.stage.spec.ts &gt; ⌨️  Keyboard Navigation Suite - STAGE</t>
-  </si>
-  <si>
-    <t>tests/ui/keyboardAccessibilityTest.stage.spec.ts</t>
+    <t>Test 4: Upload Document</t>
+  </si>
+  <si>
+    <t>chromium &gt; ui\regressionTest.stage.spec.ts &gt; 📋 Regression Suite - STAGE Environment</t>
+  </si>
+  <si>
+    <t>tests/ui/regressionTest.stage.spec.ts</t>
   </si>
   <si>
     <t xml:space="preserve">TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
 Call log:
-[2m  - waiting for locator('button:has-text("Prepare Document")') to be visible[22m
+[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
 TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
 Call log:
-[2m  - waiting for locator('button:has-text("Prepare Document")') to be visible[22m
-    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\keyboardAccessibilityTest.stage.spec.ts:461:53</t>
+[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:250:52</t>
   </si>
   <si>
     <t>Passes</t>
@@ -176,52 +176,46 @@
     <t>Avg Duration (ms)</t>
   </si>
   <si>
-    <t>Test 1: Home Page Keyboard Navigation</t>
+    <t>Test 1: Verify home page elements</t>
   </si>
   <si>
     <t>100.00%</t>
   </si>
   <si>
-    <t>14971.00</t>
-  </si>
-  <si>
-    <t>Test 2: Landing Page Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>63.00</t>
-  </si>
-  <si>
-    <t>Test 3: Signature Module Keyboard Navigation</t>
-  </si>
-  <si>
-    <t>17398.00</t>
-  </si>
-  <si>
-    <t>Test 4: Upload Document via Keyboard</t>
-  </si>
-  <si>
-    <t>30404.00</t>
-  </si>
-  <si>
-    <t>Test 5: Signature Advance Workflow via Keyboard</t>
-  </si>
-  <si>
-    <t>3198.00</t>
+    <t>15114.00</t>
+  </si>
+  <si>
+    <t>Test 2: Verify Landing Page Contents</t>
+  </si>
+  <si>
+    <t>37.00</t>
+  </si>
+  <si>
+    <t>Test 3: Verify Signature Module</t>
+  </si>
+  <si>
+    <t>20487.00</t>
   </si>
   <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>23823.00</t>
-  </si>
-  <si>
-    <t>Test 7: Create Workflow from Templates via Keyboard</t>
+    <t>18435.00</t>
+  </si>
+  <si>
+    <t>Test 5: Signature Advance Workflow</t>
   </si>
   <si>
     <t>0.00</t>
   </si>
   <si>
-    <t>Test 8: Use Workflow from Templates via Keyboard</t>
+    <t>Test 6: Sign A Document flow</t>
+  </si>
+  <si>
+    <t>Test 7: Create Workflow from Templates</t>
+  </si>
+  <si>
+    <t>Test 8: Use Workflow from Templates</t>
   </si>
 </sst>
 </file>
@@ -852,7 +846,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -861,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>17</v>
@@ -878,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
@@ -887,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>17</v>
@@ -1150,19 +1144,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="13">
+        <v>1</v>
+      </c>
+      <c r="C5" s="13">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>58</v>
-      </c>
-      <c r="B5" s="13">
-        <v>1</v>
-      </c>
-      <c r="C5" s="13">
-        <v>1</v>
-      </c>
-      <c r="D5" s="13">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>59</v>
@@ -1176,13 +1170,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="13">
         <v>0</v>
       </c>
-      <c r="E6" s="14" t="s">
-        <v>52</v>
+      <c r="E6" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>61</v>
@@ -1190,7 +1184,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B7" s="13">
         <v>1</v>
@@ -1199,18 +1193,18 @@
         <v>0</v>
       </c>
       <c r="D7" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" s="13">
         <v>1</v>
@@ -1222,15 +1216,15 @@
         <v>0</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B9" s="13">
         <v>1</v>
@@ -1242,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
+++ b/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="60">
   <si>
     <t>Metric</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Total Passed</t>
   </si>
   <si>
-    <t>3</t>
+    <t>0</t>
   </si>
   <si>
     <t>Total Failed</t>
@@ -62,25 +62,25 @@
     <t>Total Skipped</t>
   </si>
   <si>
-    <t>4</t>
+    <t>7</t>
   </si>
   <si>
     <t>Overall Pass Rate</t>
   </si>
   <si>
-    <t>37.50%</t>
+    <t>0.00%</t>
   </si>
   <si>
     <t>Total Execution Time (hrs)</t>
   </si>
   <si>
-    <t>0.02</t>
+    <t>0.01</t>
   </si>
   <si>
     <t>Average Test Duration (ms)</t>
   </si>
   <si>
-    <t>6759.13</t>
+    <t>4458.13</t>
   </si>
   <si>
     <t>Date</t>
@@ -110,7 +110,7 @@
     <t>2026-05-13</t>
   </si>
   <si>
-    <t>54.07</t>
+    <t>35.66</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -149,64 +149,49 @@
     <t>Error Details</t>
   </si>
   <si>
+    <t>Test 1: Verify home page elements</t>
+  </si>
+  <si>
+    <t>chromium &gt; ui\regressionTest.stage.spec.ts &gt; 📋 Regression Suite - STAGE Environment</t>
+  </si>
+  <si>
+    <t>tests/ui/regressionTest.stage.spec.ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: page.goto: Target page, context or browser has been closed
+Call log:
+[2m  - navigating to "https://app.selisestage.com/login", waiting until "load"[22m
+Error: page.goto: Target page, context or browser has been closed
+Call log:
+[2m  - navigating to "https://app.selisestage.com/login", waiting until "load"[22m
+    at Object.page (C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\src\pages\basePage.ts:151:24)</t>
+  </si>
+  <si>
+    <t>Passes</t>
+  </si>
+  <si>
+    <t>Success Rate</t>
+  </si>
+  <si>
+    <t>Avg Duration (ms)</t>
+  </si>
+  <si>
+    <t>35665.00</t>
+  </si>
+  <si>
+    <t>Test 2: Verify Landing Page Contents</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>Test 3: Verify Signature Module</t>
+  </si>
+  <si>
     <t>Test 4: Upload Document</t>
   </si>
   <si>
-    <t>chromium &gt; ui\regressionTest.stage.spec.ts &gt; 📋 Regression Suite - STAGE Environment</t>
-  </si>
-  <si>
-    <t>tests/ui/regressionTest.stage.spec.ts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
-Call log:
-[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
-TimeoutError: locator.waitFor: Timeout 10000ms exceeded.
-Call log:
-[2m  - waiting for locator('input[placeholder="Enter contract name"]') to be visible[22m
-    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:250:52</t>
-  </si>
-  <si>
-    <t>Passes</t>
-  </si>
-  <si>
-    <t>Success Rate</t>
-  </si>
-  <si>
-    <t>Avg Duration (ms)</t>
-  </si>
-  <si>
-    <t>Test 1: Verify home page elements</t>
-  </si>
-  <si>
-    <t>100.00%</t>
-  </si>
-  <si>
-    <t>15114.00</t>
-  </si>
-  <si>
-    <t>Test 2: Verify Landing Page Contents</t>
-  </si>
-  <si>
-    <t>37.00</t>
-  </si>
-  <si>
-    <t>Test 3: Verify Signature Module</t>
-  </si>
-  <si>
-    <t>20487.00</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>18435.00</t>
-  </si>
-  <si>
     <t>Test 5: Signature Advance Workflow</t>
-  </si>
-  <si>
-    <t>0.00</t>
   </si>
   <si>
     <t>Test 6: Sign A Document flow</t>
@@ -242,7 +227,7 @@
       <color rgb="FF9C0006"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,11 +264,6 @@
         <fgColor rgb="FF9B59B6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -311,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -332,9 +312,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -846,7 +823,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -855,7 +832,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>17</v>
@@ -872,7 +849,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
@@ -881,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>17</v>
@@ -1084,67 +1061,67 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="13">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="B2" s="13">
-        <v>1</v>
-      </c>
-      <c r="C2" s="13">
-        <v>1</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B3" s="13">
         <v>1</v>
       </c>
       <c r="C3" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="13">
         <v>0</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4" s="13">
         <v>1</v>
       </c>
       <c r="C4" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="13">
         <v>0</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B5" s="13">
         <v>1</v>
@@ -1153,18 +1130,18 @@
         <v>0</v>
       </c>
       <c r="D5" s="13">
-        <v>1</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>58</v>
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B6" s="13">
         <v>1</v>
@@ -1175,16 +1152,16 @@
       <c r="D6" s="13">
         <v>0</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>58</v>
+      <c r="E6" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B7" s="13">
         <v>1</v>
@@ -1195,16 +1172,16 @@
       <c r="D7" s="13">
         <v>0</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>58</v>
+      <c r="E7" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B8" s="13">
         <v>1</v>
@@ -1215,16 +1192,16 @@
       <c r="D8" s="13">
         <v>0</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>58</v>
+      <c r="E8" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B9" s="13">
         <v>1</v>
@@ -1235,11 +1212,11 @@
       <c r="D9" s="13">
         <v>0</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>58</v>
+      <c r="E9" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
+++ b/test-results/excel-reports/stage_monthly_summary_2026-05.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="85">
   <si>
     <t>Metric</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Total Execution Days</t>
   </si>
   <si>
-    <t>1</t>
+    <t>8</t>
   </si>
   <si>
     <t/>
@@ -47,13 +47,13 @@
     <t>Total Tests Executed</t>
   </si>
   <si>
-    <t>8</t>
+    <t>58</t>
   </si>
   <si>
     <t>Total Passed</t>
   </si>
   <si>
-    <t>3</t>
+    <t>23</t>
   </si>
   <si>
     <t>Total Failed</t>
@@ -62,60 +62,99 @@
     <t>Total Skipped</t>
   </si>
   <si>
-    <t>4</t>
+    <t>27</t>
   </si>
   <si>
     <t>Overall Pass Rate</t>
   </si>
   <si>
+    <t>39.66%</t>
+  </si>
+  <si>
+    <t>Total Execution Time (hrs)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Average Test Duration (ms)</t>
+  </si>
+  <si>
+    <t>15588.47</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Total Tests</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Timed Out</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Pass Rate</t>
+  </si>
+  <si>
+    <t>Duration (s)</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
     <t>37.50%</t>
   </si>
   <si>
-    <t>Total Execution Time (hrs)</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>Average Test Duration (ms)</t>
-  </si>
-  <si>
-    <t>7568.50</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Total Tests</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Timed Out</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>Pass Rate</t>
-  </si>
-  <si>
-    <t>Duration (s)</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
     <t>60.55</t>
   </si>
   <si>
+    <t>75.79</t>
+  </si>
+  <si>
+    <t>67.30</t>
+  </si>
+  <si>
+    <t>72.06</t>
+  </si>
+  <si>
+    <t>103.12</t>
+  </si>
+  <si>
+    <t>75.00%</t>
+  </si>
+  <si>
+    <t>304.47</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>42.66</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>25.00%</t>
+  </si>
+  <si>
+    <t>178.18</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
+    <t>904.13</t>
+  </si>
+  <si>
     <t>No.</t>
   </si>
   <si>
@@ -137,7 +176,64 @@
     <t>Last Error</t>
   </si>
   <si>
-    <t>No flaky tests detected!</t>
+    <t>Test 4: Upload Document</t>
+  </si>
+  <si>
+    <t>chromium &gt; ui\regressionTest.stage.spec.ts &gt; 📋 Regression Suite - STAGE Environment</t>
+  </si>
+  <si>
+    <t>tests/ui/regressionTest.stage.spec.ts</t>
+  </si>
+  <si>
+    <t>71.43%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: locator.click: Target page, context or browser has been closed
+Call log:
+[2m  - waiting for locator('button:has-text("Send Document")')[22m
+[2m    - locator resolved to &lt;button mat-button="" disabled="true" _ngcontent-arc2-c43="" data-cy="workflow-btn-SEND_DOCUMENT" class="mat-button mat-button-base workflow-btn workflow-btn-no-transform toolbar-button-class app-primary-button"&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m    2 × waiting for element to be visible, enabled and stable[22m
+[2m      - element is not enabled[22m
+[2m    - retrying click action[22m
+[2m    - waiting 20ms[22m
+[2m    2 × waiting for element to be visible, enabled and stable[22m
+[2m      - element is not enabled[22m
+[2m    - retrying click action[22m
+[2m      - waiting 100ms[22m
+[2m    73 × waiting for element to be visible, enabled and stable[22m
+[2m       - element is not enabled[22m
+[2m     - retrying click action[22m
+[2m       - waiting 500ms[22m
+Error: locator.click: Target page, context or browser has been closed
+Call log:
+[2m  - waiting for locator('button:has-text("Send Document")')[22m
+[2m    - locator resolved to &lt;button mat-button="" disabled="true" _ngcontent-arc2-c43="" data-cy="workflow-btn-SEND_DOCUMENT" class="mat-button mat-button-base workflow-btn workflow-btn-no-transform toolbar-button-class app-primary-button"&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m    2 × waiting for element to be visible, enabled and stable[22m
+[2m      - element is not enabled[22m
+[2m    - retrying click action[22m
+[2m    - waiting 20ms[22m
+[2m    2 × waiting for element to be visible, enabled and stable[22m
+[2m      - element is not enabled[22m
+[2m    - retrying click action[22m
+[2m      - waiting 100ms[22m
+[2m    73 × waiting for element to be visible, enabled and stable[22m
+[2m       - element is not enabled[22m
+[2m     - retrying click action[22m
+[2m       - waiting 500ms[22m
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:303:22</t>
+  </si>
+  <si>
+    <t>Test 3: Verify Signature Module</t>
+  </si>
+  <si>
+    <t>14.29%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: page.waitForTimeout: Target page, context or browser has been closed
+Error: page.waitForTimeout: Target page, context or browser has been closed
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:172:18</t>
   </si>
   <si>
     <t>Failures</t>
@@ -147,15 +243,6 @@
   </si>
   <si>
     <t>Error Details</t>
-  </si>
-  <si>
-    <t>Test 4: Upload Document</t>
-  </si>
-  <si>
-    <t>chromium &gt; ui\regressionTest.stage.spec.ts &gt; 📋 Regression Suite - STAGE Environment</t>
-  </si>
-  <si>
-    <t>tests/ui/regressionTest.stage.spec.ts</t>
   </si>
   <si>
     <t xml:space="preserve">Error: page.waitForTimeout: Target page, context or browser has been closed
@@ -163,6 +250,20 @@
     at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:246:16</t>
   </si>
   <si>
+    <t>Test 7: Create Workflow from Templates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: locator.scrollIntoViewIfNeeded: Element is not attached to the DOM
+Call log:
+[2m  - attempting scroll into view action[22m
+[2m    - waiting for element to be stable[22m
+Error: locator.scrollIntoViewIfNeeded: Element is not attached to the DOM
+Call log:
+[2m  - attempting scroll into view action[22m
+[2m    - waiting for element to be stable[22m
+    at C:\QA Things\SELISE Things\Project\Automation Framework\SELISE_Signature\tests\ui\regressionTest.stage.spec.ts:705:26</t>
+  </si>
+  <si>
     <t>Passes</t>
   </si>
   <si>
@@ -178,40 +279,43 @@
     <t>100.00%</t>
   </si>
   <si>
-    <t>13879.00</t>
+    <t>16178.43</t>
   </si>
   <si>
     <t>Test 2: Verify Landing Page Contents</t>
   </si>
   <si>
-    <t>978.00</t>
-  </si>
-  <si>
-    <t>Test 3: Verify Signature Module</t>
-  </si>
-  <si>
-    <t>29476.00</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>16215.00</t>
+    <t>181.29</t>
+  </si>
+  <si>
+    <t>85.71%</t>
+  </si>
+  <si>
+    <t>42867.14</t>
+  </si>
+  <si>
+    <t>39008.86</t>
   </si>
   <si>
     <t>Test 5: Signature Advance Workflow</t>
   </si>
   <si>
+    <t>4579.43</t>
+  </si>
+  <si>
+    <t>Test 6: Sign A Document flow</t>
+  </si>
+  <si>
+    <t>15358.71</t>
+  </si>
+  <si>
+    <t>9614.25</t>
+  </si>
+  <si>
+    <t>Test 8: Use Workflow from Templates</t>
+  </si>
+  <si>
     <t>0.00</t>
-  </si>
-  <si>
-    <t>Test 6: Sign A Document flow</t>
-  </si>
-  <si>
-    <t>Test 7: Create Workflow from Templates</t>
-  </si>
-  <si>
-    <t>Test 8: Use Workflow from Templates</t>
   </si>
 </sst>
 </file>
@@ -238,7 +342,7 @@
       <color rgb="FF9C0006"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,6 +384,11 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -307,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -322,6 +431,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -331,6 +446,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -800,7 +918,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -854,36 +972,218 @@
         <v>4</v>
       </c>
       <c r="G2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="5">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>4</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="5">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="5">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>4</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="5">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="5">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>5</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="8">
+        <v>58</v>
+      </c>
+      <c r="C10" s="8">
+        <v>23</v>
+      </c>
+      <c r="D10" s="8">
+        <v>8</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8">
+        <v>27</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="8">
-        <v>8</v>
-      </c>
-      <c r="C3" s="8">
-        <v>3</v>
-      </c>
-      <c r="D3" s="8">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8">
-        <v>4</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>31</v>
+      <c r="H10" s="8" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -897,7 +1197,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -912,19 +1212,19 @@
   <sheetData>
     <row r="1" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>24</v>
@@ -933,39 +1233,68 @@
         <v>25</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
+      <c r="A2" s="10">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="10">
+        <v>7</v>
+      </c>
+      <c r="F2" s="10">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>5</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="10">
+        <v>7</v>
+      </c>
+      <c r="F3" s="10">
+        <v>6</v>
+      </c>
+      <c r="G3" s="10">
+        <v>1</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -979,7 +1308,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -991,50 +1320,96 @@
     <col min="7" max="7" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="10" t="s">
+    <row r="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="13">
+        <v>5</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="13">
+        <v>2</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="13">
+        <v>1</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="11">
-        <v>1</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>47</v>
+      <c r="G4" s="13" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1058,184 +1433,184 @@
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="12" t="s">
+    <row r="1" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>50</v>
       </c>
+      <c r="C1" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="13">
-        <v>1</v>
-      </c>
-      <c r="C2" s="13">
-        <v>1</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="A2" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="15">
+        <v>7</v>
+      </c>
+      <c r="C2" s="15">
+        <v>7</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="15">
+        <v>7</v>
+      </c>
+      <c r="C3" s="15">
+        <v>7</v>
+      </c>
+      <c r="D3" s="15">
+        <v>0</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="15">
+        <v>7</v>
+      </c>
+      <c r="C4" s="15">
+        <v>6</v>
+      </c>
+      <c r="D4" s="15">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="13">
-        <v>1</v>
-      </c>
-      <c r="C3" s="13">
-        <v>1</v>
-      </c>
-      <c r="D3" s="13">
-        <v>0</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="13">
-        <v>1</v>
-      </c>
-      <c r="C4" s="13">
-        <v>1</v>
-      </c>
-      <c r="D4" s="13">
-        <v>0</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="13">
-        <v>1</v>
-      </c>
-      <c r="C5" s="13">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13">
-        <v>1</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="13" t="s">
+      <c r="B5" s="15">
+        <v>7</v>
+      </c>
+      <c r="C5" s="15">
+        <v>1</v>
+      </c>
+      <c r="D5" s="15">
+        <v>5</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>59</v>
       </c>
+      <c r="F5" s="15" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="13">
-        <v>1</v>
-      </c>
-      <c r="C6" s="13">
-        <v>0</v>
-      </c>
-      <c r="D6" s="13">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>61</v>
+      <c r="A6" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="15">
+        <v>7</v>
+      </c>
+      <c r="C6" s="15">
+        <v>1</v>
+      </c>
+      <c r="D6" s="15">
+        <v>0</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="13">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13">
-        <v>0</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>61</v>
+      <c r="A7" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="15">
+        <v>7</v>
+      </c>
+      <c r="C7" s="15">
+        <v>1</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="13">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>61</v>
+      <c r="A8" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="15">
+        <v>8</v>
+      </c>
+      <c r="C8" s="15">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
+        <v>2</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="13">
-        <v>1</v>
-      </c>
-      <c r="C9" s="13">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13">
-        <v>0</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>61</v>
+      <c r="A9" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="15">
+        <v>8</v>
+      </c>
+      <c r="C9" s="15">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15">
+        <v>0</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
